--- a/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11057" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11057" uniqueCount="976">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T13:25:16+00:00</t>
+    <t>2024-04-25T11:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1537,9 +1537,13 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+  </si>
+  <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="IDNPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1599,7 +1603,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="RPPS"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1608,7 +1612,7 @@
     <t>Practitioner.identifier:rpps.system</t>
   </si>
   <si>
-    <t>http://rpps.esante.gouv.fr</t>
+    <t>https://rpps.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:rpps.value</t>
@@ -1643,7 +1647,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="ADELI"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1652,7 +1656,7 @@
     <t>Practitioner.identifier:adeli.system</t>
   </si>
   <si>
-    <t>http://adeli.esante.gouv.fr</t>
+    <t>https://adeli.esante.gouv.fr</t>
   </si>
   <si>
     <t>Practitioner.identifier:adeli.value</t>
@@ -16816,7 +16820,7 @@
         <v>233</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>384</v>
+        <v>491</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>385</v>
@@ -16835,7 +16839,7 @@
         <v>78</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>78</v>
@@ -16853,10 +16857,10 @@
         <v>158</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16906,7 +16910,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>449</v>
@@ -16938,7 +16942,7 @@
         <v>450</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>452</v>
@@ -16954,7 +16958,7 @@
         <v>78</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>454</v>
@@ -17025,7 +17029,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>459</v>
@@ -17054,7 +17058,7 @@
         <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>461</v>
@@ -17142,7 +17146,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>468</v>
@@ -17257,7 +17261,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>475</v>
@@ -17374,13 +17378,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>78</v>
@@ -17405,7 +17409,7 @@
         <v>362</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>364</v>
@@ -17493,7 +17497,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>372</v>
@@ -17608,7 +17612,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>373</v>
@@ -17725,7 +17729,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>374</v>
@@ -17844,7 +17848,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>383</v>
@@ -17873,7 +17877,7 @@
         <v>233</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>385</v>
@@ -17892,7 +17896,7 @@
         <v>78</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>78</v>
@@ -17910,10 +17914,10 @@
         <v>158</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17963,7 +17967,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>449</v>
@@ -17995,7 +17999,7 @@
         <v>450</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>452</v>
@@ -18011,7 +18015,7 @@
         <v>78</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>454</v>
@@ -18082,7 +18086,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>459</v>
@@ -18199,7 +18203,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>468</v>
@@ -18314,7 +18318,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>475</v>
@@ -18431,13 +18435,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>78</v>
@@ -18462,7 +18466,7 @@
         <v>362</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>364</v>
@@ -18550,7 +18554,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>372</v>
@@ -18665,7 +18669,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>373</v>
@@ -18782,7 +18786,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>374</v>
@@ -18901,7 +18905,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>383</v>
@@ -18930,7 +18934,7 @@
         <v>233</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>385</v>
@@ -18949,7 +18953,7 @@
         <v>78</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>78</v>
@@ -18967,10 +18971,10 @@
         <v>158</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -19020,7 +19024,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>449</v>
@@ -19052,7 +19056,7 @@
         <v>450</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>452</v>
@@ -19068,7 +19072,7 @@
         <v>78</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>454</v>
@@ -19139,7 +19143,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>459</v>
@@ -19256,7 +19260,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>468</v>
@@ -19371,7 +19375,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>475</v>
@@ -19488,13 +19492,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>78</v>
@@ -19519,7 +19523,7 @@
         <v>362</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M139" t="s" s="2">
         <v>364</v>
@@ -19607,7 +19611,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>372</v>
@@ -19722,7 +19726,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>373</v>
@@ -19839,7 +19843,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>374</v>
@@ -19958,7 +19962,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>383</v>
@@ -19987,7 +19991,7 @@
         <v>233</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>385</v>
@@ -20006,7 +20010,7 @@
         <v>78</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>78</v>
@@ -20024,10 +20028,10 @@
         <v>158</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -20077,7 +20081,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>449</v>
@@ -20106,10 +20110,10 @@
         <v>137</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>452</v>
@@ -20144,7 +20148,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>78</v>
@@ -20194,7 +20198,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>459</v>
@@ -20223,7 +20227,7 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>461</v>
@@ -20311,7 +20315,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>468</v>
@@ -20426,7 +20430,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20543,10 +20547,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20572,67 +20576,67 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="R148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="R148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20653,21 +20657,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20690,19 +20694,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20751,7 +20755,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20769,13 +20773,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20783,10 +20787,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20898,10 +20902,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21015,13 +21019,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="B152" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="B152" t="s" s="2">
-        <v>561</v>
-      </c>
       <c r="C152" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21043,13 +21047,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21132,10 +21136,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21161,16 +21165,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21199,7 +21203,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>78</v>
@@ -21217,7 +21221,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21235,13 +21239,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21249,10 +21253,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21278,16 +21282,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21336,7 +21340,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21354,10 +21358,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21368,14 +21372,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21397,13 +21401,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21453,7 +21457,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21471,13 +21475,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21485,14 +21489,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21514,13 +21518,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21570,7 +21574,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21588,13 +21592,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21602,10 +21606,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21631,10 +21635,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21664,10 +21668,10 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>78</v>
@@ -21685,7 +21689,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21703,13 +21707,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21717,10 +21721,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21746,10 +21750,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21779,10 +21783,10 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>78</v>
@@ -21800,7 +21804,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21818,10 +21822,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21832,10 +21836,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21861,14 +21865,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21917,7 +21921,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21935,10 +21939,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21949,10 +21953,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21975,19 +21979,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22024,17 +22028,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22046,19 +22050,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22066,13 +22070,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22094,19 +22098,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22155,7 +22159,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22167,19 +22171,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22187,10 +22191,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22302,10 +22306,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22419,13 +22423,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="B164" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="C164" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22447,13 +22451,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22536,10 +22540,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22651,10 +22655,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22766,10 +22770,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22809,7 +22813,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22883,10 +22887,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22927,7 +22931,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22946,7 +22950,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -22996,13 +23000,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23024,13 +23028,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23113,10 +23117,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23228,10 +23232,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23345,10 +23349,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23376,7 +23380,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23462,10 +23466,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23577,10 +23581,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23692,10 +23696,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23809,10 +23813,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23872,7 +23876,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23922,13 +23926,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23953,7 +23957,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24039,10 +24043,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24154,10 +24158,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24269,10 +24273,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24312,7 +24316,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24386,10 +24390,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24501,13 +24505,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24618,10 +24622,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24733,10 +24737,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24848,10 +24852,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24891,7 +24895,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24965,10 +24969,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25080,13 +25084,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25111,7 +25115,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25197,10 +25201,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25312,10 +25316,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25427,10 +25431,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25470,7 +25474,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25544,10 +25548,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25659,13 +25663,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25776,10 +25780,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25891,10 +25895,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26006,10 +26010,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26049,7 +26053,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26123,10 +26127,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26238,13 +26242,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26269,7 +26273,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26355,10 +26359,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26470,10 +26474,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26585,10 +26589,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26628,7 +26632,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26702,10 +26706,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26817,13 +26821,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26848,7 +26852,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26934,10 +26938,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27049,10 +27053,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27164,10 +27168,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27207,7 +27211,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27281,10 +27285,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27396,10 +27400,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27439,7 +27443,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27513,10 +27517,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27628,10 +27632,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27657,10 +27661,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27672,7 +27676,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27690,10 +27694,10 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27711,7 +27715,7 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27720,7 +27724,7 @@
         <v>90</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27729,13 +27733,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27743,10 +27747,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27772,16 +27776,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27830,7 +27834,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27848,10 +27852,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27862,10 +27866,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27891,16 +27895,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27928,10 +27932,10 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27949,7 +27953,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27967,13 +27971,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27981,10 +27985,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28007,16 +28011,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28066,7 +28070,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28098,10 +28102,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28127,10 +28131,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28181,7 +28185,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28202,7 +28206,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28213,10 +28217,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28239,19 +28243,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28300,7 +28304,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28318,13 +28322,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28332,10 +28336,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28361,14 +28365,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28396,10 +28400,10 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>78</v>
@@ -28417,7 +28421,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28435,13 +28439,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28449,10 +28453,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28475,17 +28479,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28534,7 +28538,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28552,13 +28556,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28566,10 +28570,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28592,17 +28596,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28651,7 +28655,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28672,10 +28676,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28683,10 +28687,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28709,13 +28713,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28754,7 +28758,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28764,7 +28768,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28782,13 +28786,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28796,10 +28800,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28911,10 +28915,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29028,14 +29032,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29057,10 +29061,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29115,7 +29119,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29147,10 +29151,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29176,14 +29180,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29232,7 +29236,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29253,7 +29257,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29264,10 +29268,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29293,10 +29297,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29327,7 +29331,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>78</v>
@@ -29345,7 +29349,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29366,10 +29370,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29377,10 +29381,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29406,14 +29410,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29462,7 +29466,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29483,10 +29487,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29494,10 +29498,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29523,10 +29527,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29577,7 +29581,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29598,7 +29602,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29609,13 +29613,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29637,13 +29641,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29694,7 +29698,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29712,13 +29716,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29726,10 +29730,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29841,10 +29845,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29954,13 +29958,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -29982,13 +29986,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30071,10 +30075,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30186,10 +30190,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30303,13 +30307,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B232" t="s" s="2">
         <v>850</v>
       </c>
-      <c r="B232" t="s" s="2">
-        <v>849</v>
-      </c>
       <c r="C232" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30420,10 +30424,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30535,10 +30539,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30650,10 +30654,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30693,7 +30697,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30767,10 +30771,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30830,7 +30834,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30880,13 +30884,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -30997,10 +31001,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31112,10 +31116,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31227,10 +31231,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31270,7 +31274,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31344,10 +31348,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31407,7 +31411,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31457,13 +31461,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31574,10 +31578,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31689,10 +31693,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31804,10 +31808,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31847,7 +31851,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31921,10 +31925,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31984,7 +31988,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32034,10 +32038,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32077,7 +32081,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32151,10 +32155,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32266,14 +32270,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32295,10 +32299,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32353,7 +32357,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32385,10 +32389,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32414,14 +32418,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32470,7 +32474,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32491,7 +32495,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32502,10 +32506,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32531,10 +32535,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32565,7 +32569,7 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32583,7 +32587,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32604,10 +32608,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32615,10 +32619,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32730,10 +32734,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32847,10 +32851,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32922,14 +32926,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32964,13 +32968,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33033,7 +33037,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33083,13 +33087,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33152,7 +33156,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33202,10 +33206,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33321,10 +33325,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33350,14 +33354,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33406,7 +33410,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33427,10 +33431,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33438,10 +33442,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33553,10 +33557,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33670,10 +33674,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33699,7 +33703,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33787,10 +33791,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33816,7 +33820,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33906,10 +33910,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33932,13 +33936,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -33989,7 +33993,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34010,7 +34014,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34021,13 +34025,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34049,13 +34053,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34106,7 +34110,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34124,13 +34128,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34138,10 +34142,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34253,10 +34257,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34370,14 +34374,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34399,10 +34403,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34457,7 +34461,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34489,10 +34493,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34518,14 +34522,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34574,7 +34578,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34595,7 +34599,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34606,10 +34610,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34635,10 +34639,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34669,7 +34673,7 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>78</v>
@@ -34687,7 +34691,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34708,10 +34712,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34719,10 +34723,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34834,10 +34838,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34951,10 +34955,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35026,14 +35030,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35068,13 +35072,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35099,7 +35103,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35137,7 +35141,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35187,10 +35191,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35218,7 +35222,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35306,10 +35310,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35425,10 +35429,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35454,14 +35458,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35510,7 +35514,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35531,10 +35535,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35542,10 +35546,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35657,10 +35661,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35774,10 +35778,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35803,7 +35807,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35891,10 +35895,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35920,7 +35924,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36010,10 +36014,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36039,10 +36043,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36093,7 +36097,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36114,7 +36118,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36125,13 +36129,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36153,13 +36157,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36210,7 +36214,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36228,13 +36232,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36242,10 +36246,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36357,10 +36361,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36474,14 +36478,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36503,10 +36507,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36561,7 +36565,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36593,10 +36597,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36622,14 +36626,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36678,7 +36682,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36699,7 +36703,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36710,10 +36714,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36739,10 +36743,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36773,7 +36777,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>78</v>
@@ -36791,7 +36795,7 @@
         <v>78</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36806,16 +36810,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36823,10 +36827,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36938,10 +36942,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37055,10 +37059,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37130,7 +37134,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37172,13 +37176,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37203,7 +37207,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37241,7 +37245,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37291,13 +37295,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37322,7 +37326,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37360,7 +37364,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37410,10 +37414,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37529,10 +37533,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37558,14 +37562,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37614,7 +37618,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37635,10 +37639,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37646,10 +37650,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37761,10 +37765,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37878,10 +37882,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37907,7 +37911,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37978,7 +37982,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -37995,10 +37999,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38024,7 +38028,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38097,7 +38101,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38114,10 +38118,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38143,10 +38147,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38197,7 +38201,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38218,7 +38222,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38229,10 +38233,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38255,19 +38259,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38296,7 +38300,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38314,7 +38318,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38332,10 +38336,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:50:43+00:00</t>
+    <t>2024-04-26T07:42:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
